--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484022_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484022_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8205</v>
+        <v>5.6202</v>
       </c>
       <c r="E2" t="n">
-        <v>9.488200000000001</v>
+        <v>9.6526</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.6677</v>
+        <v>-4.0324</v>
       </c>
       <c r="G2" t="n">
         <v>6.2645</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3576</v>
+        <v>0.1573</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1813</v>
+        <v>-0.0169</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5389</v>
+        <v>0.1742</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6032</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9485</v>
+        <v>3.5738</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0957</v>
+        <v>3.2067</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8528</v>
+        <v>0.3671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9355</v>
+        <v>2.8214</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3462</v>
+        <v>0.9117</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4107</v>
+        <v>1.9096</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6488</v>
+        <v>4.805</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5283</v>
+        <v>1.4315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1205</v>
+        <v>3.3736</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-1.9837</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1821</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5312</v>
+        <v>-1.4639</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7935</v>
+        <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2647</v>
+        <v>-0.6362</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3627</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.098</v>
+        <v>-0.0298</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9365</v>
+        <v>3.3847</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8779</v>
+        <v>2.5039</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0585</v>
+        <v>0.8809</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8214</v>
+        <v>2.9355</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9117</v>
+        <v>3.3462</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9096</v>
+        <v>-0.4107</v>
       </c>
       <c r="J4" t="n">
-        <v>4.805</v>
+        <v>3.6488</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4315</v>
+        <v>3.5283</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3736</v>
+        <v>0.1205</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9837</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.1821</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4639</v>
+        <v>-0.5312</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3887</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3806</v>
+        <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2736</v>
+        <v>0.1714</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9352</v>
+        <v>0.0454</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3384</v>
+        <v>0.1261</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1338</v>
+        <v>2.1232</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5831</v>
+        <v>3.32</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4493</v>
+        <v>-1.1968</v>
       </c>
       <c r="G5" t="n">
         <v>1.602</v>
@@ -844,13 +844,13 @@
         <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3337</v>
+        <v>-0.3443</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6858</v>
+        <v>0.0511</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6479</v>
+        <v>-0.3954</v>
       </c>
       <c r="V5" t="n">
         <v>1.0639</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9614</v>
+        <v>0.6746</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2624</v>
+        <v>-0.0501</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8909</v>
+        <v>0.5735</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8909</v>
+        <v>0.7808</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.2073</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8909</v>
+        <v>1.8195</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8909</v>
+        <v>1.094</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.7255</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.246</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.3132</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.9328</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9758</v>
+        <v>-1.1903</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5936</v>
+        <v>0.051</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7208</v>
+        <v>0.0454</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8728</v>
+        <v>0.0056</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0704</v>
+        <v>-0.5592</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2041</v>
+        <v>0.2607</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2745</v>
+        <v>-0.8199</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5735</v>
+        <v>-0.4166</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7808</v>
+        <v>0.3374</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2073</v>
+        <v>-0.754</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8195</v>
+        <v>1.1113</v>
       </c>
       <c r="K8" t="n">
-        <v>1.094</v>
+        <v>1.0686</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7255</v>
+        <v>0.0427</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.246</v>
+        <v>-1.5278</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3132</v>
+        <v>-0.7311</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9328</v>
+        <v>-0.7967</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6439</v>
+        <v>0.0043</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4251</v>
+        <v>-0.1247</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2188</v>
+        <v>0.1289</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,31 +1111,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3498</v>
+        <v>-0.6383</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4421</v>
+        <v>-0.9837</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7919</v>
+        <v>0.3454</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4166</v>
+        <v>-2.0067</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3374</v>
+        <v>-1.2903</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.754</v>
+        <v>-0.7164</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1113</v>
+        <v>-0.4789</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0686</v>
+        <v>-0.5592</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0427</v>
+        <v>0.0803</v>
       </c>
       <c r="M9" t="n">
         <v>-1.5278</v>
@@ -1147,37 +1147,37 @@
         <v>-0.7967</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2137</v>
+        <v>-0.2862</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0567</v>
+        <v>-0.0963</v>
       </c>
       <c r="U9" t="n">
-        <v>0.157</v>
+        <v>-0.1899</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9405</v>
+        <v>0.266</v>
       </c>
       <c r="W9" t="n">
-        <v>0.266</v>
+        <v>-0.4085</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2065</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,75 +1189,71 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9109</v>
+        <v>-1.3075</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3125</v>
+        <v>-0.671</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4015</v>
+        <v>-0.6364</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0067</v>
+        <v>1.8909</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2903</v>
+        <v>1.8909</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7164</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4789</v>
+        <v>1.8909</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5592</v>
+        <v>1.8909</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0803</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5278</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7311</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3887</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5589</v>
+        <v>1.5871</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4251</v>
+        <v>1.0883</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1338</v>
+        <v>0.4988</v>
       </c>
       <c r="V10" t="n">
-        <v>0.266</v>
+        <v>-1.8097</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4085</v>
+        <v>-0.6745</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6745</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>M. MAÑES CARRETERO</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1267,64 +1263,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6086</v>
+        <v>-1.3477</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0696</v>
+        <v>0.2894</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5391</v>
+        <v>-1.6371</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.2803</v>
+        <v>-1.9202</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5168</v>
+        <v>-0.7063</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7635</v>
+        <v>-1.2139</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6197</v>
+        <v>0.4027</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2175</v>
+        <v>0.2823</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8372</v>
+        <v>0.1205</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6606</v>
+        <v>-2.3229</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7343</v>
+        <v>-0.9885</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9263</v>
+        <v>-1.3344</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2137</v>
+        <v>-0.221</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7481</v>
+        <v>0.0851</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5344</v>
+        <v>-0.3061</v>
       </c>
       <c r="V11" t="n">
-        <v>3.2821</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.2821</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1341,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1446</v>
+        <v>-1.3477</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.283</v>
+        <v>0.2894</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8616</v>
+        <v>-1.6371</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9202</v>
@@ -1390,13 +1386,13 @@
         <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.018</v>
+        <v>-0.221</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4874</v>
+        <v>0.0851</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5306</v>
+        <v>-0.3061</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1409,7 +1405,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>M. MAÑES CARRETERO</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1419,64 +1419,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1446</v>
+        <v>-1.6344</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.283</v>
+        <v>-0.8428</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8616</v>
+        <v>-0.7916</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.9202</v>
+        <v>-4.2803</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7063</v>
+        <v>-1.5168</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2139</v>
+        <v>-2.7635</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4027</v>
+        <v>-1.6197</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2823</v>
+        <v>0.2175</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1205</v>
+        <v>-1.8372</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3229</v>
+        <v>-2.6606</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9885</v>
+        <v>-1.7343</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3344</v>
+        <v>-0.9263</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7935</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.018</v>
+        <v>-0.2395</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4874</v>
+        <v>-0.5214</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5306</v>
+        <v>0.2819</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.2821</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.2821</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1497,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.1665</v>
+        <v>-2.3657</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6802</v>
+        <v>-1.9636</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4863</v>
+        <v>-0.4022</v>
       </c>
       <c r="G14" t="n">
         <v>-2.3303</v>
@@ -1542,13 +1542,13 @@
         <v>0.9919</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1639</v>
+        <v>-0.0354</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2438</v>
+        <v>-0.0396</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0799</v>
+        <v>0.0042</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.2272</v>
+        <v>-2.8829</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5026</v>
+        <v>-0.2985</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7246</v>
+        <v>-2.5843</v>
       </c>
       <c r="G15" t="n">
         <v>-1.8871</v>
@@ -1620,13 +1620,13 @@
         <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6773</v>
+        <v>-0.333</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4988</v>
+        <v>-0.2947</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1786</v>
+        <v>-0.0383</v>
       </c>
       <c r="V15" t="n">
         <v>-0.266</v>
@@ -1653,16 +1653,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2968</v>
+        <v>3.623999999999998</v>
       </c>
       <c r="E16" t="n">
-        <v>13.9155</v>
+        <v>15.8316</v>
       </c>
       <c r="F16" t="n">
-        <v>-12.6191</v>
+        <v>-12.2074</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4320999999999999</v>
+        <v>0.4321000000000017</v>
       </c>
       <c r="H16" t="n">
         <v>2.391200000000002</v>
@@ -1689,7 +1689,7 @@
         <v>-13.9657</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7932999999999999</v>
+        <v>0.7932999999999997</v>
       </c>
       <c r="Q16" t="n">
         <v>-16.069</v>
@@ -1698,13 +1698,13 @@
         <v>16.8626</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.9451</v>
+        <v>-0.6175999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.5273</v>
+        <v>-0.6113</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4178999999999999</v>
+        <v>-0.006299999999999951</v>
       </c>
       <c r="V16" t="n">
         <v>3.0161</v>
@@ -1731,13 +1731,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4519</v>
+        <v>6.32</v>
       </c>
       <c r="E17" t="n">
-        <v>8.007199999999999</v>
+        <v>8.823399999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5553</v>
+        <v>-2.5034</v>
       </c>
       <c r="G17" t="n">
         <v>5.4576</v>
@@ -1776,13 +1776,13 @@
         <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1015</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9352</v>
+        <v>-0.1189</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8337</v>
+        <v>0.8855</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1026</v>
@@ -1809,13 +1809,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.3478</v>
+        <v>3.326</v>
       </c>
       <c r="E18" t="n">
-        <v>4.4223</v>
+        <v>2.9938</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9255</v>
+        <v>0.3321</v>
       </c>
       <c r="G18" t="n">
         <v>-2.0769</v>
@@ -1854,13 +1854,13 @@
         <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>3.0279</v>
+        <v>1.0061</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9103</v>
+        <v>0.4819</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1176</v>
+        <v>0.5242</v>
       </c>
       <c r="V18" t="n">
         <v>2.4129</v>
@@ -1965,13 +1965,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1813</v>
+        <v>0.2374</v>
       </c>
       <c r="E20" t="n">
         <v>0.921</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7396</v>
+        <v>-0.6835</v>
       </c>
       <c r="G20" t="n">
         <v>0.4538</v>
@@ -2010,13 +2010,13 @@
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4954</v>
+        <v>-0.4393</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3707</v>
+        <v>-0.3146</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1738</v>
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8626</v>
+        <v>-1.7784</v>
       </c>
       <c r="E23" t="n">
         <v>-3.0216</v>
       </c>
       <c r="F23" t="n">
-        <v>1.159</v>
+        <v>1.2432</v>
       </c>
       <c r="G23" t="n">
         <v>-0.847</v>
@@ -2244,13 +2244,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4642</v>
+        <v>0.5484</v>
       </c>
       <c r="T23" t="n">
         <v>0.3061</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1581</v>
+        <v>0.2423</v>
       </c>
       <c r="V23" t="n">
         <v>-1.083</v>
@@ -2277,13 +2277,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5694</v>
+        <v>-1.845</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2199</v>
+        <v>0.3923</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3495</v>
+        <v>-2.2373</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8913</v>
@@ -2322,13 +2322,13 @@
         <v>1.3887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9171</v>
+        <v>-0.1927</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8105</v>
+        <v>-0.1983</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1066</v>
+        <v>0.0056</v>
       </c>
       <c r="V24" t="n">
         <v>1.0326</v>
@@ -2343,7 +2343,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2355,73 +2355,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7198</v>
+        <v>-2.5969</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7334000000000001</v>
+        <v>1.5359</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9864</v>
+        <v>-4.1328</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.0101</v>
+        <v>-0.8631</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.3534</v>
+        <v>-0.9175</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6567</v>
+        <v>0.0543</v>
       </c>
       <c r="J25" t="n">
-        <v>2.588</v>
+        <v>2.327</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4595</v>
+        <v>0.5497</v>
       </c>
       <c r="L25" t="n">
-        <v>2.1286</v>
+        <v>1.7773</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.5982</v>
+        <v>-3.1901</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.8129</v>
+        <v>-1.4671</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.7853</v>
+        <v>-1.723</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.3645</v>
+        <v>-0.3968</v>
       </c>
       <c r="R25" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S25" t="n">
-        <v>2.0513</v>
+        <v>0.0326</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0431</v>
+        <v>-0.323</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0082</v>
+        <v>0.3556</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.7771</v>
+        <v>-3.3534</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.0713</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.7771</v>
+        <v>-3.2821</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>I. FERNANDEZ MASIP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2433,73 +2433,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.7659</v>
+        <v>-4.1184</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9238</v>
+        <v>-3.54</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.6897</v>
+        <v>-0.5784</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.8631</v>
+        <v>-1.46</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9175</v>
+        <v>-1.0533</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0543</v>
+        <v>-0.4067</v>
       </c>
       <c r="J26" t="n">
-        <v>2.327</v>
+        <v>0.6548</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5497</v>
+        <v>0.4138</v>
       </c>
       <c r="L26" t="n">
-        <v>1.7773</v>
+        <v>0.241</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.1901</v>
+        <v>-2.1148</v>
       </c>
       <c r="N26" t="n">
         <v>-1.4671</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.723</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P26" t="n">
+        <v>-2.579</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-4.1661</v>
+      </c>
+      <c r="R26" t="n">
         <v>1.5871</v>
       </c>
-      <c r="Q26" t="n">
-        <v>-0.3968</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.9838</v>
-      </c>
       <c r="S26" t="n">
-        <v>-1.1364</v>
+        <v>-0.0794</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9352</v>
+        <v>-0.2947</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2013</v>
+        <v>0.2153</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.3534</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.0713</v>
+        <v>0.266</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.2821</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MASIP</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2511,67 +2511,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.7951</v>
+        <v>-4.5963</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.744</v>
+        <v>-1.5496</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0511</v>
+        <v>-3.0467</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.46</v>
+        <v>-3.0101</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.0533</v>
+        <v>-2.3534</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4067</v>
+        <v>-0.6567</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6548</v>
+        <v>2.588</v>
       </c>
       <c r="K27" t="n">
-        <v>0.4138</v>
+        <v>0.4595</v>
       </c>
       <c r="L27" t="n">
-        <v>0.241</v>
+        <v>2.1286</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.1148</v>
+        <v>-5.5982</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.4671</v>
+        <v>-2.8129</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-2.7853</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.579</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q27" t="n">
-        <v>-4.1661</v>
+        <v>-4.3645</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5871</v>
+        <v>2.3806</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.7561</v>
+        <v>1.1747</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4988</v>
+        <v>0.2268</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2574</v>
+        <v>0.9479</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>-0.7771</v>
       </c>
       <c r="W27" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.266</v>
+        <v>-0.7771</v>
       </c>
     </row>
     <row r="28">
@@ -2589,13 +2589,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.441499999999998</v>
+        <v>-2.7613</v>
       </c>
       <c r="E28" t="n">
-        <v>10.7575</v>
+        <v>10.7573</v>
       </c>
       <c r="F28" t="n">
-        <v>-14.1988</v>
+        <v>-13.5185</v>
       </c>
       <c r="G28" t="n">
         <v>-2.352199999999999</v>
@@ -2604,7 +2604,7 @@
         <v>-3.097399999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7453999999999998</v>
+        <v>0.7453999999999997</v>
       </c>
       <c r="J28" t="n">
         <v>23.5491</v>
@@ -2625,7 +2625,7 @@
         <v>-11.886</v>
       </c>
       <c r="P28" t="n">
-        <v>0.000100000000000211</v>
+        <v>0.0001000000000006551</v>
       </c>
       <c r="Q28" t="n">
         <v>-15.8708</v>
@@ -2634,13 +2634,13 @@
         <v>15.8708</v>
       </c>
       <c r="S28" t="n">
-        <v>1.927199999999999</v>
+        <v>2.6073</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1128000000000001</v>
+        <v>-0.1127000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>2.0398</v>
+        <v>2.72</v>
       </c>
       <c r="V28" t="n">
         <v>-3.0162</v>
